--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ae0a7a05
-	0x7ff6ae0a7a60
-	0x7ff6ade216ad
-	0x7ff6ade7a13e
-	0x7ff6ade7a44c
-	0x7ff6adecebe7
-	0x7ff6adecb8fb
-	0x7ff6ade6b068
-	0x7ff6ade6be93
-	0x7ff6ae3629a0
-	0x7ff6ae35ce20
-	0x7ff6ae37cc15
-	0x7ff6ae0c309e
-	0x7ff6ae0cad8f
-	0x7ff6ae0b0be4
-	0x7ff6ae0b0d9f
-	0x7ff6ae0967f8
+	0x7ff7df807a05
+	0x7ff7df807a60
+	0x7ff7df5816ad
+	0x7ff7df5da13e
+	0x7ff7df5da44c
+	0x7ff7df62ebe7
+	0x7ff7df62b8fb
+	0x7ff7df5cb068
+	0x7ff7df5cbe93
+	0x7ff7dfac29a0
+	0x7ff7dfabce20
+	0x7ff7dfadcc15
+	0x7ff7df82309e
+	0x7ff7df82ad8f
+	0x7ff7df810be4
+	0x7ff7df810d9f
+	0x7ff7df7f67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
